--- a/用卷/xlsx/常规科目/1977.xlsx
+++ b/用卷/xlsx/常规科目/1977.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\常规科目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F134D5F-08C3-4747-BA42-1349B27A966E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6342A1E1-78CC-4D6E-A8C3-5C816114160D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
   <si>
     <t>年份</t>
   </si>
@@ -223,6 +223,22 @@
   </si>
   <si>
     <t>河南卷,北京卷文理,天津卷文理,河北卷,山西卷,内蒙古卷文理,辽宁卷,吉林卷,黑龙江卷,上海卷文理,南通卷,江苏卷,浙江卷,安徽卷文理,福建卷,江西卷,山东卷,湖北卷,株洲卷,湖南卷,广东卷,百色卷文理,广西卷文理,四川卷,贵州卷,云南卷,西藏卷,陕西卷,甘肃卷,青海卷,宁夏卷,新疆卷文理</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南卷,北京卷文理,天津卷,河北卷,山西卷,内蒙古卷文理,辽宁卷,吉林卷,黑龙江卷,上海卷文理,南通卷,江苏卷文理,浙江卷,安徽卷文理,福建卷文理,江西卷,山东卷,湖北卷,株洲卷,湖南卷,广东卷,百色卷,广西卷,四川卷,贵州卷,云南卷,西藏卷,陕西卷,甘肃卷,青海卷,宁夏卷,新疆卷文理</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少39</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少40</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少32</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -353,7 +369,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -365,9 +381,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -715,18 +728,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="23"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="18"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -738,33 +751,33 @@
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="16">
+      <c r="A4" s="15">
         <v>1977</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="9"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1977</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -775,10 +788,10 @@
       <c r="B6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -787,10 +800,10 @@
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -799,22 +812,22 @@
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>1977</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -822,13 +835,13 @@
       <c r="A10" s="1">
         <v>1977</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
@@ -837,10 +850,10 @@
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -849,48 +862,48 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="10"/>
+      <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="11">
-        <v>1977</v>
-      </c>
-      <c r="B13" s="16" t="s">
+      <c r="A13" s="10">
+        <v>1977</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="11">
-        <v>1977</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="10">
+        <v>1977</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="6"/>
+      <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>1977</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="15"/>
+      <c r="D15" s="14"/>
     </row>
     <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -899,22 +912,22 @@
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="15"/>
+      <c r="D16" s="14"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>1977</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -925,10 +938,10 @@
       <c r="B18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -939,22 +952,22 @@
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="9"/>
+      <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="11">
-        <v>1977</v>
-      </c>
-      <c r="B20" s="16" t="s">
+      <c r="A20" s="10">
+        <v>1977</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -963,58 +976,58 @@
       <c r="B21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="11">
-        <v>1977</v>
-      </c>
-      <c r="B22" s="16" t="s">
+      <c r="A22" s="10">
+        <v>1977</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="11"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>1977</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="10"/>
+      <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>1977</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="15"/>
+      <c r="D24" s="14"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="11">
-        <v>1977</v>
-      </c>
-      <c r="B25" s="16" t="s">
+      <c r="A25" s="10">
+        <v>1977</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1022,13 +1035,13 @@
       <c r="A26" s="1">
         <v>1977</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1039,10 +1052,10 @@
       <c r="B27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="9"/>
+      <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
@@ -1051,10 +1064,10 @@
       <c r="B28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="12"/>
+      <c r="D28" s="11"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
@@ -1063,10 +1076,10 @@
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="9"/>
+      <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
@@ -1075,10 +1088,10 @@
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="11"/>
+      <c r="D30" s="10"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
@@ -1087,22 +1100,22 @@
       <c r="B31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="11"/>
+      <c r="D31" s="10"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>1977</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="9"/>
+      <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
@@ -1111,10 +1124,10 @@
       <c r="B33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="8"/>
+      <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
@@ -1123,38 +1136,38 @@
       <c r="B34" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="11"/>
+      <c r="D34" s="10"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="9">
-        <v>1977</v>
-      </c>
-      <c r="B35" s="9" t="s">
+      <c r="A35" s="8">
+        <v>1977</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="7"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="6"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
@@ -1166,91 +1179,91 @@
       <c r="C38" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="7"/>
+      <c r="D38" s="6"/>
     </row>
     <row r="39" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="4">
-        <v>32</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="7"/>
+      <c r="B39" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="6"/>
     </row>
     <row r="40" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="4">
-        <v>40</v>
-      </c>
-      <c r="C40" s="6" t="s">
+      <c r="B40" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="7"/>
+      <c r="D40" s="6"/>
     </row>
     <row r="41" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="4">
-        <v>32</v>
-      </c>
-      <c r="C41" s="6" t="s">
+      <c r="B41" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="7"/>
+      <c r="D41" s="6"/>
     </row>
     <row r="42" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B42" s="4">
-        <v>32</v>
-      </c>
-      <c r="C42" s="6" t="s">
+      <c r="B42" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="17"/>
+      <c r="D42" s="16"/>
     </row>
     <row r="43" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="4">
-        <v>32</v>
-      </c>
-      <c r="C43" s="6" t="s">
+      <c r="B43" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="7"/>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="4">
-        <v>32</v>
-      </c>
-      <c r="C44" s="6" t="s">
+      <c r="B44" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="7"/>
+      <c r="D44" s="6"/>
     </row>
     <row r="45" spans="1:4" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="4">
-        <v>32</v>
-      </c>
-      <c r="C45" s="6" t="s">
+      <c r="B45" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="7"/>
+      <c r="D45" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
